--- a/python/第四问新/第四问新_数据采集建议.xlsx
+++ b/python/第四问新/第四问新_数据采集建议.xlsx
@@ -504,7 +504,7 @@
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="D2" s="5" t="n">
-        <v>88.00000000000001</v>
+        <v>88</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>0</v>
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>87.33333333333334</v>
+        <v>87.333333</v>
       </c>
       <c r="E3" s="6" t="n">
         <v>0.3333333333333333</v>
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="D4" s="5" t="n">
-        <v>86.66666666666667</v>
+        <v>86.666667</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>0</v>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>86.00000000000001</v>
+        <v>86</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>0</v>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>82.66666666666667</v>
+        <v>82.666667</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>0</v>
@@ -843,7 +843,7 @@
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>81.33333333333334</v>
+        <v>81.333333</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -879,20 +879,20 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
           <t>逐笔报损、折价处理与损耗原因</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>第三批—持续完善</t>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>第二批—近期建设</t>
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>81.33333333333333</v>
+        <v>81.333333</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>0</v>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>76.66666666666666</v>
+        <v>76.666667</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>0</v>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>75.33333333333334</v>
+        <v>75.333333</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>0</v>
@@ -2435,7 +2435,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>按综合优先级得分排序，前3名/第4—6名/第7名以后</t>
+          <t>采用并列排名后，排名≤3/4≤排名≤6/排名≥7</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>第一批立即建设，第二批近期建设，第三批持续完善；批次仅表示落地顺序，不再增加另一套分级。</t>
+          <t>同分项目共享名次并进入同一批次，因此批次数量不强制为3、3、3；批次仅表示落地顺序。</t>
         </is>
       </c>
     </row>
@@ -2628,10 +2628,10 @@
         <v>3</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>2.666666666666667</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>3</v>
@@ -2710,7 +2710,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>7</v>
@@ -2719,7 +2719,7 @@
         <v>6</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>6.666666666666667</v>
+        <v>6.333333333333333</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0</v>
@@ -2786,7 +2786,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
@@ -2879,8 +2879,8 @@
           <t>库存、缺货与陈列状态</t>
         </is>
       </c>
-      <c r="B2" s="6" t="n">
-        <v>88.00000000000001</v>
+      <c r="B2" s="3" t="n">
+        <v>88</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>1</v>
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>87.33333333333334</v>
+        <v>87.333333</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>2</v>
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>86.66666666666667</v>
+        <v>86.666667</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>3</v>
@@ -3023,8 +3023,8 @@
           <t>客流、天气、节假日与竞品价格</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
-        <v>86.00000000000001</v>
+      <c r="B5" s="3" t="n">
+        <v>86</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>4</v>
@@ -3072,7 +3072,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>82.66666666666667</v>
+        <v>82.666667</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>5</v>
@@ -3116,11 +3116,11 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>匿名顾客、订单与购物篮</t>
+          <t>逐笔报损、折价处理与损耗原因</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>81.33333333333334</v>
+        <v>81.333333</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>6</v>
@@ -3131,22 +3131,22 @@
         </is>
       </c>
       <c r="E7" s="6" t="n">
-        <v>80.63429014356483</v>
+        <v>80.77342964638163</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>2.10649739940651</v>
+        <v>1.925511893044435</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>76.45405915382601</v>
+        <v>76.90377466628516</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>84.59247159792037</v>
+        <v>84.36525538222791</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>6.231</v>
+        <v>6.166</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>1.063462314898615</v>
+        <v>0.9171303684925504</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>4</v>
@@ -3155,7 +3155,7 @@
         <v>8</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0055</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>10000</v>
@@ -3164,37 +3164,37 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>逐笔报损、折价处理与损耗原因</t>
+          <t>匿名顾客、订单与购物篮</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>81.33333333333333</v>
+        <v>81.333333</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>第三批—持续完善</t>
+          <t>第二批—近期建设</t>
         </is>
       </c>
       <c r="E8" s="6" t="n">
-        <v>80.77342964638163</v>
+        <v>80.63429014356483</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>1.925511893044435</v>
+        <v>2.10649739940651</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>76.90377466628516</v>
+        <v>76.45405915382601</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>84.36525538222791</v>
+        <v>84.59247159792037</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>6.166</v>
+        <v>6.231</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.9171303684925504</v>
+        <v>1.063462314898615</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>4</v>
@@ -3203,7 +3203,7 @@
         <v>8</v>
       </c>
       <c r="M8" s="9" t="n">
-        <v>0.0055</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>10000</v>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>76.66666666666666</v>
+        <v>76.666667</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>8</v>
@@ -3264,7 +3264,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>75.33333333333334</v>
+        <v>75.333333</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>9</v>

--- a/python/第四问新/第四问新_数据采集建议.xlsx
+++ b/python/第四问新/第四问新_数据采集建议.xlsx
@@ -67,22 +67,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
+        <fgColor rgb="00839FB3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
+        <fgColor rgb="00E8D2D2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00EEE2C8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAF7"/>
+        <fgColor rgb="00D9E4EC"/>
       </patternFill>
     </fill>
   </fills>
